--- a/docs/karta-svyazey-prototipa.xlsx
+++ b/docs/karta-svyazey-prototipa.xlsx
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Реестр'!$A$1:$N$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Навигация'!$A$1:$K$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Связи'!$A$1:$K$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Связи'!$A$1:$K$139</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -3222,7 +3222,7 @@
       <c r="M33" s="27" t="n"/>
       <c r="N33" s="27" t="inlineStr">
         <is>
-          <t>Вкладки: история, предстоящие, заметки, важное. «Написать» нет</t>
+          <t>Вкладки: история, предстоящие, заметки, важное. «Написать» нет. «Архивировать» убрана 25.09.2026: архива клиентов нет в паспорте, записи и история не удаляются</t>
         </is>
       </c>
     </row>
@@ -6805,7 +6805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K140"/>
+  <dimension ref="A1:K139"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" style="12" min="1" max="1"/>
@@ -10877,7 +10877,11 @@
           <t>Связано</t>
         </is>
       </c>
-      <c r="K80" s="27" t="n"/>
+      <c r="K80" s="27" t="inlineStr">
+        <is>
+          <t>Кнопка не показывалась у клиентов вне чёрного списка (неверное условие). Исправлено 25.09.2026</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="13">
       <c r="A81" s="27" t="inlineStr">
@@ -13747,17 +13751,17 @@
     <row r="136" ht="23.85" customHeight="1" s="13">
       <c r="A136" s="27" t="inlineStr">
         <is>
-          <t>L-249</t>
+          <t>L-250</t>
         </is>
       </c>
       <c r="B136" s="27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>SYS</t>
         </is>
       </c>
       <c r="C136" s="27" t="inlineStr">
         <is>
-          <t>A-09</t>
+          <t>SYS-01</t>
         </is>
       </c>
       <c r="D136" s="29">
@@ -13766,31 +13770,27 @@
       </c>
       <c r="E136" s="27" t="inlineStr">
         <is>
-          <t>Кнопка «Архивировать»</t>
+          <t>Ссылка «Мои записи» (авторизован)</t>
         </is>
       </c>
       <c r="F136" s="27" t="inlineStr">
         <is>
-          <t>Закрыть оверлей</t>
+          <t>Переход</t>
         </is>
       </c>
       <c r="G136" s="27" t="inlineStr">
         <is>
-          <t>A-09</t>
+          <t>CAB-01</t>
         </is>
       </c>
       <c r="H136" s="29">
         <f>IF(G136="ANCHOR","Прокрутка к секции",IF(G136="EXT","Внешняя ссылка",IF(G136="PARENT","Вернуться туда, откуда открыто",IFERROR(INDEX(Реестр!$C:$C,MATCH(G136,Реестр!$A:$A,0)),"⚠ нет в реестре"))))</f>
         <v/>
       </c>
-      <c r="I136" s="27" t="inlineStr">
-        <is>
-          <t>Демо-тост</t>
-        </is>
-      </c>
+      <c r="I136" s="27" t="n"/>
       <c r="J136" s="28" t="inlineStr">
         <is>
-          <t>Требует решения</t>
+          <t>Связано</t>
         </is>
       </c>
       <c r="K136" s="27" t="inlineStr">
@@ -13802,7 +13802,7 @@
     <row r="137" ht="15" customHeight="1" s="13">
       <c r="A137" s="27" t="inlineStr">
         <is>
-          <t>L-250</t>
+          <t>L-251</t>
         </is>
       </c>
       <c r="B137" s="27" t="inlineStr">
@@ -13812,7 +13812,7 @@
       </c>
       <c r="C137" s="27" t="inlineStr">
         <is>
-          <t>SYS-01</t>
+          <t>SYS-05</t>
         </is>
       </c>
       <c r="D137" s="29">
@@ -13821,17 +13821,17 @@
       </c>
       <c r="E137" s="27" t="inlineStr">
         <is>
-          <t>Ссылка «Мои записи» (авторизован)</t>
+          <t>Телефон студии</t>
         </is>
       </c>
       <c r="F137" s="27" t="inlineStr">
         <is>
-          <t>Переход</t>
+          <t>Внешняя ссылка</t>
         </is>
       </c>
       <c r="G137" s="27" t="inlineStr">
         <is>
-          <t>CAB-01</t>
+          <t>EXT</t>
         </is>
       </c>
       <c r="H137" s="29">
@@ -13853,17 +13853,17 @@
     <row r="138" ht="15" customHeight="1" s="13">
       <c r="A138" s="27" t="inlineStr">
         <is>
-          <t>L-251</t>
+          <t>L-252</t>
         </is>
       </c>
       <c r="B138" s="27" t="inlineStr">
         <is>
-          <t>SYS</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C138" s="27" t="inlineStr">
         <is>
-          <t>SYS-05</t>
+          <t>A-33</t>
         </is>
       </c>
       <c r="D138" s="29">
@@ -13872,17 +13872,17 @@
       </c>
       <c r="E138" s="27" t="inlineStr">
         <is>
-          <t>Телефон студии</t>
+          <t>Кнопки карточек A-S1/A-S2 («Обновить», «Повторить», «Отмена»)</t>
         </is>
       </c>
       <c r="F138" s="27" t="inlineStr">
         <is>
-          <t>Внешняя ссылка</t>
+          <t>Переход</t>
         </is>
       </c>
       <c r="G138" s="27" t="inlineStr">
         <is>
-          <t>EXT</t>
+          <t>A-01</t>
         </is>
       </c>
       <c r="H138" s="29">
@@ -13904,7 +13904,7 @@
     <row r="139" ht="15" customHeight="1" s="13">
       <c r="A139" s="27" t="inlineStr">
         <is>
-          <t>L-252</t>
+          <t>L-253</t>
         </is>
       </c>
       <c r="B139" s="27" t="inlineStr">
@@ -13923,7 +13923,7 @@
       </c>
       <c r="E139" s="27" t="inlineStr">
         <is>
-          <t>Кнопки карточек A-S1/A-S2 («Обновить», «Повторить», «Отмена»)</t>
+          <t>Кнопки карточек SYS-03/SYS-04 («Войти», «Выйти»)</t>
         </is>
       </c>
       <c r="F139" s="27" t="inlineStr">
@@ -13933,7 +13933,7 @@
       </c>
       <c r="G139" s="27" t="inlineStr">
         <is>
-          <t>A-01</t>
+          <t>AUTH-04</t>
         </is>
       </c>
       <c r="H139" s="29">
@@ -13952,57 +13952,7 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="15" customHeight="1" s="13">
-      <c r="A140" s="27" t="inlineStr">
-        <is>
-          <t>L-253</t>
-        </is>
-      </c>
-      <c r="B140" s="27" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C140" s="27" t="inlineStr">
-        <is>
-          <t>A-33</t>
-        </is>
-      </c>
-      <c r="D140" s="29">
-        <f>IFERROR(INDEX(Реестр!$C:$C,MATCH(C140,Реестр!$A:$A,0)),"⚠ нет в реестре")</f>
-        <v/>
-      </c>
-      <c r="E140" s="27" t="inlineStr">
-        <is>
-          <t>Кнопки карточек SYS-03/SYS-04 («Войти», «Выйти»)</t>
-        </is>
-      </c>
-      <c r="F140" s="27" t="inlineStr">
-        <is>
-          <t>Переход</t>
-        </is>
-      </c>
-      <c r="G140" s="27" t="inlineStr">
-        <is>
-          <t>AUTH-04</t>
-        </is>
-      </c>
-      <c r="H140" s="29">
-        <f>IF(G140="ANCHOR","Прокрутка к секции",IF(G140="EXT","Внешняя ссылка",IF(G140="PARENT","Вернуться туда, откуда открыто",IFERROR(INDEX(Реестр!$C:$C,MATCH(G140,Реестр!$A:$A,0)),"⚠ нет в реестре"))))</f>
-        <v/>
-      </c>
-      <c r="I140" s="27" t="n"/>
-      <c r="J140" s="28" t="inlineStr">
-        <is>
-          <t>Связано</t>
-        </is>
-      </c>
-      <c r="K140" s="27" t="inlineStr">
-        <is>
-          <t>Есть в прототипе, не было в карте</t>
-        </is>
-      </c>
-    </row>
+    <row r="140" ht="15" customHeight="1" s="13"/>
     <row r="141" ht="15" customHeight="1" s="13"/>
     <row r="142" ht="15" customHeight="1" s="13"/>
     <row r="143" ht="15" customHeight="1" s="13"/>
@@ -14118,7 +14068,7 @@
     <row r="253" ht="15" customHeight="1" s="13"/>
     <row r="254" ht="15" customHeight="1" s="13"/>
   </sheetData>
-  <autoFilter ref="A1:K140"/>
+  <autoFilter ref="A1:K139"/>
   <conditionalFormatting sqref="H2:H1000">
     <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="5" text="" percent="0" bottom="0">
       <formula>LEFT(H2,1)="⚠"</formula>

--- a/docs/karta-svyazey-prototipa.xlsx
+++ b/docs/karta-svyazey-prototipa.xlsx
@@ -16,9 +16,9 @@
     <sheet name="Вопросы" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Реестр'!$A$1:$N$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Реестр'!$A$1:$N$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Навигация'!$A$1:$K$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Связи'!$A$1:$K$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Связи'!$A$1:$K$149</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -1172,7 +1172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N57"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="12" min="1" max="1"/>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="N3" s="27" t="inlineStr">
         <is>
-          <t>Своя простая шапка: «← Назад» и логотип. Шапки лендинга с якорями нет</t>
+          <t>Своя простая шапка: «← Назад» и логотип. Шапки лендинга с якорями нет · 25.09.2026: блок «Работы мастера» — опубликованные фото из A-12; цены по уровню мастера</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2868,7 @@
       <c r="M27" s="27" t="n"/>
       <c r="N27" s="27" t="inlineStr">
         <is>
-          <t>Кнопки: «Перенести», «Визит завершён», «Отметить неявку», «Отменить», «Открыть карточку клиента». «Подтвердить» и «Принять оплату» нет</t>
+          <t>Кнопки: «Перенести», «Визит завершён», «Отметить неявку», «Отменить», «Открыть карточку клиента». «Подтвердить» и «Принять оплату» нет · 25.09.2026: у завершённой записи — «Фото работ» (A-12); время записи показывает уборку до …</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       <c r="M33" s="27" t="n"/>
       <c r="N33" s="27" t="inlineStr">
         <is>
-          <t>Вкладки: история, предстоящие, заметки, важное. «Написать» нет. «Архивировать» убрана 25.09.2026: архива клиентов нет в паспорте, записи и история не удаляются</t>
+          <t>Вкладки: история, предстоящие, заметки, важное. «Написать» нет. «Архивировать» убрана 25.09.2026: архива клиентов нет в паспорте, записи и история не удаляются · 25.09.2026: в истории визитов — «N фото» / «+ Добавить фото» (A-12)</t>
         </is>
       </c>
     </row>
@@ -3405,7 +3405,7 @@
       <c r="M36" s="27" t="n"/>
       <c r="N36" s="27" t="inlineStr">
         <is>
-          <t>Клик по ячейке — рабочий день / выходной</t>
+          <t>Клик по ячейке — рабочий день / выходной · 25.09.2026: под сеткой — блок «Особые дни студии» (A-20d), особые дни отмечены рамкой</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3470,7 @@
       <c r="M37" s="27" t="n"/>
       <c r="N37" s="27" t="inlineStr">
         <is>
-          <t>Услуги и график — только просмотр</t>
+          <t>Услуги и график — только просмотр · 25.09.2026: переключатель уровня «Мастер / Топ-мастер», цены услуг по уровню, «Новый график с даты» (A-22p)</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       <c r="M39" s="27" t="n"/>
       <c r="N39" s="27" t="inlineStr">
         <is>
-          <t>Открывается из списка (строка услуги, «+ Добавить услугу») и по прямому адресу; «Сохранить», «Отмена», «← Услуги» возвращают к списку. Исправлено 25.09.2026</t>
+          <t>Открывается из списка (строка услуги, «+ Добавить услугу») и по прямому адресу; «Сохранить», «Отмена», «← Услуги» возвращают к списку. Исправлено 25.09.2026 · 25.09.2026: добавлены поля «Уборка после услуги, мин» и «Цена у топ-мастера, ₽» с проверкой «не ниже цены у мастера»</t>
         </is>
       </c>
     </row>
@@ -4722,9 +4722,201 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1" s="13"/>
-    <row r="59" ht="15" customHeight="1" s="13"/>
-    <row r="60" ht="15" customHeight="1" s="13"/>
+    <row r="58" ht="15" customHeight="1" s="13">
+      <c r="A58" s="27" t="inlineStr">
+        <is>
+          <t>A-12</t>
+        </is>
+      </c>
+      <c r="B58" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C58" s="27" t="inlineStr">
+        <is>
+          <t>Фото работ визита (загрузка, согласие клиента, публикация в галерее)</t>
+        </is>
+      </c>
+      <c r="D58" s="27" t="inlineStr">
+        <is>
+          <t>Модалка</t>
+        </is>
+      </c>
+      <c r="E58" s="27" t="inlineStr">
+        <is>
+          <t>Администратор</t>
+        </is>
+      </c>
+      <c r="F58" s="27" t="inlineStr">
+        <is>
+          <t>A-09</t>
+        </is>
+      </c>
+      <c r="G58" s="27" t="n"/>
+      <c r="H58" s="28" t="inlineStr">
+        <is>
+          <t>Диалог «Фото работ» — из поповера завершённой записи и из истории визитов</t>
+        </is>
+      </c>
+      <c r="I58" s="28" t="inlineStr">
+        <is>
+          <t>Совпадает</t>
+        </is>
+      </c>
+      <c r="J58" s="29">
+        <f>COUNTIF(Связи!$C:$C,A58)+IF(G58="",0,COUNTIF(Навигация!$B:$B,G58))</f>
+        <v/>
+      </c>
+      <c r="K58" s="29">
+        <f>COUNTIF(Связи!$G:$G,A58)+COUNTIF(Навигация!$F:$F,A58)</f>
+        <v/>
+      </c>
+      <c r="L58" s="29">
+        <f>IF(D58="Дизайн-система","вне графа",IF(AND(K58=0,OR(D58="Состояние",D58="Служебная")),"демо / вход по событию",IF(K58=0,"⚠ сирота",IF(J58=0,"⚠ тупик","ок"))))</f>
+        <v/>
+      </c>
+      <c r="M58" s="27" t="inlineStr">
+        <is>
+          <t>Добавлено 25.09.2026 по схеме БД (work_photos)</t>
+        </is>
+      </c>
+      <c r="N58" s="27" t="inlineStr">
+        <is>
+          <t>Загрузка фото, подпись, отметки «Клиент разрешил публикацию» и «В галерее «Наши работы»». Без согласия опубликовать нельзя. Опубликованные фото — в профиле мастера (PUB-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1" s="13">
+      <c r="A59" s="27" t="inlineStr">
+        <is>
+          <t>A-20d</t>
+        </is>
+      </c>
+      <c r="B59" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C59" s="27" t="inlineStr">
+        <is>
+          <t>Особые дни студии (праздники, санитарные, сокращённые и дополнительные рабочие дни)</t>
+        </is>
+      </c>
+      <c r="D59" s="27" t="inlineStr">
+        <is>
+          <t>Панель</t>
+        </is>
+      </c>
+      <c r="E59" s="27" t="inlineStr">
+        <is>
+          <t>Администратор</t>
+        </is>
+      </c>
+      <c r="F59" s="27" t="inlineStr">
+        <is>
+          <t>A-20</t>
+        </is>
+      </c>
+      <c r="G59" s="27" t="n"/>
+      <c r="H59" s="28" t="inlineStr">
+        <is>
+          <t>Блок «Особые дни студии» на #/staff/admin/masters/schedule</t>
+        </is>
+      </c>
+      <c r="I59" s="28" t="inlineStr">
+        <is>
+          <t>Совпадает</t>
+        </is>
+      </c>
+      <c r="J59" s="29">
+        <f>COUNTIF(Связи!$C:$C,A59)+IF(G59="",0,COUNTIF(Навигация!$B:$B,G59))</f>
+        <v/>
+      </c>
+      <c r="K59" s="29">
+        <f>COUNTIF(Связи!$G:$G,A59)+COUNTIF(Навигация!$F:$F,A59)</f>
+        <v/>
+      </c>
+      <c r="L59" s="29">
+        <f>IF(D59="Дизайн-система","вне графа",IF(AND(K59=0,OR(D59="Состояние",D59="Служебная")),"демо / вход по событию",IF(K59=0,"⚠ сирота",IF(J59=0,"⚠ тупик","ок"))))</f>
+        <v/>
+      </c>
+      <c r="M59" s="27" t="inlineStr">
+        <is>
+          <t>Добавлено 25.09.2026 по схеме БД (studio_day_overrides)</t>
+        </is>
+      </c>
+      <c r="N59" s="27" t="inlineStr">
+        <is>
+          <t>Список с «Удалить» и форма «Добавить особый день». До сохранения показывает записи, которые не помещаются в новый режим. В сетке смен особый день отмечен рамкой</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1" s="13">
+      <c r="A60" s="27" t="inlineStr">
+        <is>
+          <t>A-22p</t>
+        </is>
+      </c>
+      <c r="B60" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C60" s="27" t="inlineStr">
+        <is>
+          <t>Новый график мастера с даты</t>
+        </is>
+      </c>
+      <c r="D60" s="27" t="inlineStr">
+        <is>
+          <t>Панель</t>
+        </is>
+      </c>
+      <c r="E60" s="27" t="inlineStr">
+        <is>
+          <t>Администратор</t>
+        </is>
+      </c>
+      <c r="F60" s="27" t="inlineStr">
+        <is>
+          <t>A-22</t>
+        </is>
+      </c>
+      <c r="G60" s="27" t="n"/>
+      <c r="H60" s="28" t="inlineStr">
+        <is>
+          <t>Форма «Новый график с даты» в карточке мастера</t>
+        </is>
+      </c>
+      <c r="I60" s="28" t="inlineStr">
+        <is>
+          <t>Совпадает</t>
+        </is>
+      </c>
+      <c r="J60" s="29">
+        <f>COUNTIF(Связи!$C:$C,A60)+IF(G60="",0,COUNTIF(Навигация!$B:$B,G60))</f>
+        <v/>
+      </c>
+      <c r="K60" s="29">
+        <f>COUNTIF(Связи!$G:$G,A60)+COUNTIF(Навигация!$F:$F,A60)</f>
+        <v/>
+      </c>
+      <c r="L60" s="29">
+        <f>IF(D60="Дизайн-система","вне графа",IF(AND(K60=0,OR(D60="Состояние",D60="Служебная")),"демо / вход по событию",IF(K60=0,"⚠ сирота",IF(J60=0,"⚠ тупик","ок"))))</f>
+        <v/>
+      </c>
+      <c r="M60" s="27" t="inlineStr">
+        <is>
+          <t>Добавлено 25.09.2026 по схеме БД (master_weekly_hours.valid_from)</t>
+        </is>
+      </c>
+      <c r="N60" s="27" t="inlineStr">
+        <is>
+          <t>Дата начала, рабочие дни (пн и вс недоступны), часы смены. Показывает записи, которые не попадают в новый график. После сохранения — блок «Новый график с …» и «Отменить изменение»</t>
+        </is>
+      </c>
+    </row>
     <row r="61" ht="15" customHeight="1" s="13"/>
     <row r="62" ht="15" customHeight="1" s="13"/>
     <row r="63" ht="15" customHeight="1" s="13"/>
@@ -4773,7 +4965,7 @@
     <row r="106" ht="15" customHeight="1" s="13"/>
     <row r="107" ht="15" customHeight="1" s="13"/>
   </sheetData>
-  <autoFilter ref="A1:N57"/>
+  <autoFilter ref="A1:N60"/>
   <conditionalFormatting sqref="L2:L500">
     <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="5" text="" percent="0" bottom="0">
       <formula>LEFT(L2,1)="⚠"</formula>
@@ -6805,7 +6997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K139"/>
+  <dimension ref="A1:K149"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" style="12" min="1" max="1"/>
@@ -13952,16 +14144,528 @@
         </is>
       </c>
     </row>
-    <row r="140" ht="15" customHeight="1" s="13"/>
-    <row r="141" ht="15" customHeight="1" s="13"/>
-    <row r="142" ht="15" customHeight="1" s="13"/>
-    <row r="143" ht="15" customHeight="1" s="13"/>
-    <row r="144" ht="15" customHeight="1" s="13"/>
-    <row r="145" ht="23.85" customHeight="1" s="13"/>
-    <row r="146" ht="15" customHeight="1" s="13"/>
-    <row r="147" ht="15" customHeight="1" s="13"/>
-    <row r="148" ht="15" customHeight="1" s="13"/>
-    <row r="149" ht="23.85" customHeight="1" s="13"/>
+    <row r="140" ht="15" customHeight="1" s="13">
+      <c r="A140" s="27" t="inlineStr">
+        <is>
+          <t>L-254</t>
+        </is>
+      </c>
+      <c r="B140" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C140" s="27" t="inlineStr">
+        <is>
+          <t>A-20</t>
+        </is>
+      </c>
+      <c r="D140" s="29">
+        <f>IFERROR(INDEX(Реестр!$C:$C,MATCH(C140,Реестр!$A:$A,0)),"⚠ нет в реестре")</f>
+        <v/>
+      </c>
+      <c r="E140" s="27" t="inlineStr">
+        <is>
+          <t>Блок «Особые дни студии» под сеткой смен</t>
+        </is>
+      </c>
+      <c r="F140" s="27" t="inlineStr">
+        <is>
+          <t>Панель</t>
+        </is>
+      </c>
+      <c r="G140" s="27" t="inlineStr">
+        <is>
+          <t>A-20d</t>
+        </is>
+      </c>
+      <c r="H140" s="29">
+        <f>IF(G140="ANCHOR","Прокрутка к секции",IF(G140="EXT","Внешняя ссылка",IF(G140="PARENT","Вернуться туда, откуда открыто",IFERROR(INDEX(Реестр!$C:$C,MATCH(G140,Реестр!$A:$A,0)),"⚠ нет в реестре"))))</f>
+        <v/>
+      </c>
+      <c r="I140" s="27" t="n"/>
+      <c r="J140" s="28" t="inlineStr">
+        <is>
+          <t>Связано</t>
+        </is>
+      </c>
+      <c r="K140" s="27" t="inlineStr">
+        <is>
+          <t>Блок всегда виден под сеткой</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="15" customHeight="1" s="13">
+      <c r="A141" s="27" t="inlineStr">
+        <is>
+          <t>L-255</t>
+        </is>
+      </c>
+      <c r="B141" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C141" s="27" t="inlineStr">
+        <is>
+          <t>A-20d</t>
+        </is>
+      </c>
+      <c r="D141" s="29">
+        <f>IFERROR(INDEX(Реестр!$C:$C,MATCH(C141,Реестр!$A:$A,0)),"⚠ нет в реестре")</f>
+        <v/>
+      </c>
+      <c r="E141" s="27" t="inlineStr">
+        <is>
+          <t>Кнопка «Добавить день»</t>
+        </is>
+      </c>
+      <c r="F141" s="27" t="inlineStr">
+        <is>
+          <t>Переход</t>
+        </is>
+      </c>
+      <c r="G141" s="27" t="inlineStr">
+        <is>
+          <t>A-20</t>
+        </is>
+      </c>
+      <c r="H141" s="29">
+        <f>IF(G141="ANCHOR","Прокрутка к секции",IF(G141="EXT","Внешняя ссылка",IF(G141="PARENT","Вернуться туда, откуда открыто",IFERROR(INDEX(Реестр!$C:$C,MATCH(G141,Реестр!$A:$A,0)),"⚠ нет в реестре"))))</f>
+        <v/>
+      </c>
+      <c r="I141" s="27" t="inlineStr">
+        <is>
+          <t>Сетка смен обновляется: особый день отмечен рамкой</t>
+        </is>
+      </c>
+      <c r="J141" s="28" t="inlineStr">
+        <is>
+          <t>Связано</t>
+        </is>
+      </c>
+      <c r="K141" s="27" t="inlineStr">
+        <is>
+          <t>Тост с числом записей, требующих решения</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="15" customHeight="1" s="13">
+      <c r="A142" s="27" t="inlineStr">
+        <is>
+          <t>L-256</t>
+        </is>
+      </c>
+      <c r="B142" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C142" s="27" t="inlineStr">
+        <is>
+          <t>A-20d</t>
+        </is>
+      </c>
+      <c r="D142" s="29">
+        <f>IFERROR(INDEX(Реестр!$C:$C,MATCH(C142,Реестр!$A:$A,0)),"⚠ нет в реестре")</f>
+        <v/>
+      </c>
+      <c r="E142" s="27" t="inlineStr">
+        <is>
+          <t>Кнопка «Удалить» у особого дня</t>
+        </is>
+      </c>
+      <c r="F142" s="27" t="inlineStr">
+        <is>
+          <t>Переход</t>
+        </is>
+      </c>
+      <c r="G142" s="27" t="inlineStr">
+        <is>
+          <t>A-20</t>
+        </is>
+      </c>
+      <c r="H142" s="29">
+        <f>IF(G142="ANCHOR","Прокрутка к секции",IF(G142="EXT","Внешняя ссылка",IF(G142="PARENT","Вернуться туда, откуда открыто",IFERROR(INDEX(Реестр!$C:$C,MATCH(G142,Реестр!$A:$A,0)),"⚠ нет в реестре"))))</f>
+        <v/>
+      </c>
+      <c r="I142" s="27" t="n"/>
+      <c r="J142" s="28" t="inlineStr">
+        <is>
+          <t>Связано</t>
+        </is>
+      </c>
+      <c r="K142" s="27" t="inlineStr">
+        <is>
+          <t>День возвращается к обычному режиму</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="15" customHeight="1" s="13">
+      <c r="A143" s="27" t="inlineStr">
+        <is>
+          <t>L-257</t>
+        </is>
+      </c>
+      <c r="B143" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C143" s="27" t="inlineStr">
+        <is>
+          <t>A-22</t>
+        </is>
+      </c>
+      <c r="D143" s="29">
+        <f>IFERROR(INDEX(Реестр!$C:$C,MATCH(C143,Реестр!$A:$A,0)),"⚠ нет в реестре")</f>
+        <v/>
+      </c>
+      <c r="E143" s="27" t="inlineStr">
+        <is>
+          <t>Кнопка «Новый график с даты»</t>
+        </is>
+      </c>
+      <c r="F143" s="27" t="inlineStr">
+        <is>
+          <t>Панель</t>
+        </is>
+      </c>
+      <c r="G143" s="27" t="inlineStr">
+        <is>
+          <t>A-22p</t>
+        </is>
+      </c>
+      <c r="H143" s="29">
+        <f>IF(G143="ANCHOR","Прокрутка к секции",IF(G143="EXT","Внешняя ссылка",IF(G143="PARENT","Вернуться туда, откуда открыто",IFERROR(INDEX(Реестр!$C:$C,MATCH(G143,Реестр!$A:$A,0)),"⚠ нет в реестре"))))</f>
+        <v/>
+      </c>
+      <c r="I143" s="27" t="n"/>
+      <c r="J143" s="28" t="inlineStr">
+        <is>
+          <t>Связано</t>
+        </is>
+      </c>
+      <c r="K143" s="27" t="inlineStr">
+        <is>
+          <t>Кнопка в блоке «График работы»</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="15" customHeight="1" s="13">
+      <c r="A144" s="27" t="inlineStr">
+        <is>
+          <t>L-258</t>
+        </is>
+      </c>
+      <c r="B144" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C144" s="27" t="inlineStr">
+        <is>
+          <t>A-22p</t>
+        </is>
+      </c>
+      <c r="D144" s="29">
+        <f>IFERROR(INDEX(Реестр!$C:$C,MATCH(C144,Реестр!$A:$A,0)),"⚠ нет в реестре")</f>
+        <v/>
+      </c>
+      <c r="E144" s="27" t="inlineStr">
+        <is>
+          <t>Кнопка «Сохранить график»</t>
+        </is>
+      </c>
+      <c r="F144" s="27" t="inlineStr">
+        <is>
+          <t>Закрыть оверлей</t>
+        </is>
+      </c>
+      <c r="G144" s="27" t="inlineStr">
+        <is>
+          <t>A-22</t>
+        </is>
+      </c>
+      <c r="H144" s="29">
+        <f>IF(G144="ANCHOR","Прокрутка к секции",IF(G144="EXT","Внешняя ссылка",IF(G144="PARENT","Вернуться туда, откуда открыто",IFERROR(INDEX(Реестр!$C:$C,MATCH(G144,Реестр!$A:$A,0)),"⚠ нет в реестре"))))</f>
+        <v/>
+      </c>
+      <c r="I144" s="27" t="inlineStr">
+        <is>
+          <t>В карточке появляется блок «Новый график с …»</t>
+        </is>
+      </c>
+      <c r="J144" s="28" t="inlineStr">
+        <is>
+          <t>Связано</t>
+        </is>
+      </c>
+      <c r="K144" s="27" t="inlineStr">
+        <is>
+          <t>Проверки: дата не раньше завтра, есть рабочий день, смена в 10:00–20:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="15" customHeight="1" s="13">
+      <c r="A145" s="27" t="inlineStr">
+        <is>
+          <t>L-259</t>
+        </is>
+      </c>
+      <c r="B145" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C145" s="27" t="inlineStr">
+        <is>
+          <t>A-22p</t>
+        </is>
+      </c>
+      <c r="D145" s="29">
+        <f>IFERROR(INDEX(Реестр!$C:$C,MATCH(C145,Реестр!$A:$A,0)),"⚠ нет в реестре")</f>
+        <v/>
+      </c>
+      <c r="E145" s="27" t="inlineStr">
+        <is>
+          <t>Кнопка «Отмена»</t>
+        </is>
+      </c>
+      <c r="F145" s="27" t="inlineStr">
+        <is>
+          <t>Закрыть оверлей</t>
+        </is>
+      </c>
+      <c r="G145" s="27" t="inlineStr">
+        <is>
+          <t>A-22</t>
+        </is>
+      </c>
+      <c r="H145" s="29">
+        <f>IF(G145="ANCHOR","Прокрутка к секции",IF(G145="EXT","Внешняя ссылка",IF(G145="PARENT","Вернуться туда, откуда открыто",IFERROR(INDEX(Реестр!$C:$C,MATCH(G145,Реестр!$A:$A,0)),"⚠ нет в реестре"))))</f>
+        <v/>
+      </c>
+      <c r="I145" s="27" t="n"/>
+      <c r="J145" s="28" t="inlineStr">
+        <is>
+          <t>Связано</t>
+        </is>
+      </c>
+      <c r="K145" s="27" t="inlineStr">
+        <is>
+          <t>Добавлено 25.09.2026 вместе с экраном</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="15" customHeight="1" s="13">
+      <c r="A146" s="27" t="inlineStr">
+        <is>
+          <t>L-260</t>
+        </is>
+      </c>
+      <c r="B146" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C146" s="27" t="inlineStr">
+        <is>
+          <t>A-03</t>
+        </is>
+      </c>
+      <c r="D146" s="29">
+        <f>IFERROR(INDEX(Реестр!$C:$C,MATCH(C146,Реестр!$A:$A,0)),"⚠ нет в реестре")</f>
+        <v/>
+      </c>
+      <c r="E146" s="27" t="inlineStr">
+        <is>
+          <t>Кнопка «Фото работ» (у завершённой записи)</t>
+        </is>
+      </c>
+      <c r="F146" s="27" t="inlineStr">
+        <is>
+          <t>Модалка</t>
+        </is>
+      </c>
+      <c r="G146" s="27" t="inlineStr">
+        <is>
+          <t>A-12</t>
+        </is>
+      </c>
+      <c r="H146" s="29">
+        <f>IF(G146="ANCHOR","Прокрутка к секции",IF(G146="EXT","Внешняя ссылка",IF(G146="PARENT","Вернуться туда, откуда открыто",IFERROR(INDEX(Реестр!$C:$C,MATCH(G146,Реестр!$A:$A,0)),"⚠ нет в реестре"))))</f>
+        <v/>
+      </c>
+      <c r="I146" s="27" t="n"/>
+      <c r="J146" s="28" t="inlineStr">
+        <is>
+          <t>Связано</t>
+        </is>
+      </c>
+      <c r="K146" s="27" t="inlineStr">
+        <is>
+          <t>Только для статуса «Завершена»</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="15" customHeight="1" s="13">
+      <c r="A147" s="27" t="inlineStr">
+        <is>
+          <t>L-261</t>
+        </is>
+      </c>
+      <c r="B147" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C147" s="27" t="inlineStr">
+        <is>
+          <t>A-09</t>
+        </is>
+      </c>
+      <c r="D147" s="29">
+        <f>IFERROR(INDEX(Реестр!$C:$C,MATCH(C147,Реестр!$A:$A,0)),"⚠ нет в реестре")</f>
+        <v/>
+      </c>
+      <c r="E147" s="27" t="inlineStr">
+        <is>
+          <t>Ссылка «N фото» / «+ Добавить фото» в истории визитов</t>
+        </is>
+      </c>
+      <c r="F147" s="27" t="inlineStr">
+        <is>
+          <t>Модалка</t>
+        </is>
+      </c>
+      <c r="G147" s="27" t="inlineStr">
+        <is>
+          <t>A-12</t>
+        </is>
+      </c>
+      <c r="H147" s="29">
+        <f>IF(G147="ANCHOR","Прокрутка к секции",IF(G147="EXT","Внешняя ссылка",IF(G147="PARENT","Вернуться туда, откуда открыто",IFERROR(INDEX(Реестр!$C:$C,MATCH(G147,Реестр!$A:$A,0)),"⚠ нет в реестре"))))</f>
+        <v/>
+      </c>
+      <c r="I147" s="27" t="n"/>
+      <c r="J147" s="28" t="inlineStr">
+        <is>
+          <t>Связано</t>
+        </is>
+      </c>
+      <c r="K147" s="27" t="inlineStr">
+        <is>
+          <t>Только у завершённых визитов</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="15" customHeight="1" s="13">
+      <c r="A148" s="27" t="inlineStr">
+        <is>
+          <t>L-262</t>
+        </is>
+      </c>
+      <c r="B148" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C148" s="27" t="inlineStr">
+        <is>
+          <t>A-12</t>
+        </is>
+      </c>
+      <c r="D148" s="29">
+        <f>IFERROR(INDEX(Реестр!$C:$C,MATCH(C148,Реестр!$A:$A,0)),"⚠ нет в реестре")</f>
+        <v/>
+      </c>
+      <c r="E148" s="27" t="inlineStr">
+        <is>
+          <t>Кнопка «Готово» / крестик / клик по фону</t>
+        </is>
+      </c>
+      <c r="F148" s="27" t="inlineStr">
+        <is>
+          <t>Закрыть оверлей</t>
+        </is>
+      </c>
+      <c r="G148" s="27" t="inlineStr">
+        <is>
+          <t>PARENT</t>
+        </is>
+      </c>
+      <c r="H148" s="29">
+        <f>IF(G148="ANCHOR","Прокрутка к секции",IF(G148="EXT","Внешняя ссылка",IF(G148="PARENT","Вернуться туда, откуда открыто",IFERROR(INDEX(Реестр!$C:$C,MATCH(G148,Реестр!$A:$A,0)),"⚠ нет в реестре"))))</f>
+        <v/>
+      </c>
+      <c r="I148" s="27" t="n"/>
+      <c r="J148" s="28" t="inlineStr">
+        <is>
+          <t>Связано</t>
+        </is>
+      </c>
+      <c r="K148" s="27" t="inlineStr">
+        <is>
+          <t>Добавлено 25.09.2026 вместе с экраном</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="15" customHeight="1" s="13">
+      <c r="A149" s="27" t="inlineStr">
+        <is>
+          <t>L-263</t>
+        </is>
+      </c>
+      <c r="B149" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C149" s="27" t="inlineStr">
+        <is>
+          <t>A-12</t>
+        </is>
+      </c>
+      <c r="D149" s="29">
+        <f>IFERROR(INDEX(Реестр!$C:$C,MATCH(C149,Реестр!$A:$A,0)),"⚠ нет в реестре")</f>
+        <v/>
+      </c>
+      <c r="E149" s="27" t="inlineStr">
+        <is>
+          <t>Ссылка «Профиль мастера →»</t>
+        </is>
+      </c>
+      <c r="F149" s="27" t="inlineStr">
+        <is>
+          <t>Переход</t>
+        </is>
+      </c>
+      <c r="G149" s="27" t="inlineStr">
+        <is>
+          <t>PUB-05</t>
+        </is>
+      </c>
+      <c r="H149" s="29">
+        <f>IF(G149="ANCHOR","Прокрутка к секции",IF(G149="EXT","Внешняя ссылка",IF(G149="PARENT","Вернуться туда, откуда открыто",IFERROR(INDEX(Реестр!$C:$C,MATCH(G149,Реестр!$A:$A,0)),"⚠ нет в реестре"))))</f>
+        <v/>
+      </c>
+      <c r="I149" s="27" t="inlineStr">
+        <is>
+          <t>Опубликованные фото — в блоке «Работы мастера»</t>
+        </is>
+      </c>
+      <c r="J149" s="28" t="inlineStr">
+        <is>
+          <t>Связано</t>
+        </is>
+      </c>
+      <c r="K149" s="27" t="inlineStr">
+        <is>
+          <t>Добавлено 25.09.2026 вместе с экраном</t>
+        </is>
+      </c>
+    </row>
     <row r="150" ht="23.85" customHeight="1" s="13"/>
     <row r="151" ht="15" customHeight="1" s="13"/>
     <row r="152" ht="15" customHeight="1" s="13"/>
@@ -14068,7 +14772,7 @@
     <row r="253" ht="15" customHeight="1" s="13"/>
     <row r="254" ht="15" customHeight="1" s="13"/>
   </sheetData>
-  <autoFilter ref="A1:K139"/>
+  <autoFilter ref="A1:K149"/>
   <conditionalFormatting sqref="H2:H1000">
     <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="5" text="" percent="0" bottom="0">
       <formula>LEFT(H2,1)="⚠"</formula>
@@ -14101,7 +14805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="12" min="1" max="1"/>
@@ -14398,9 +15102,96 @@
       </c>
       <c r="F10" s="28" t="n"/>
     </row>
-    <row r="11" ht="15" customHeight="1" s="13"/>
-    <row r="12" ht="15" customHeight="1" s="13"/>
-    <row r="13" ht="23.85" customHeight="1" s="13"/>
+    <row r="11" ht="15" customHeight="1" s="13">
+      <c r="A11" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>Администратор</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>Особый день студии (санитарный день)</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>A-01 → [меню: Мастера] → A-19 → A-20 → A-20d → [Добавить день] → A-20</t>
+        </is>
+      </c>
+      <c r="E11" s="28" t="inlineStr">
+        <is>
+          <t>Проходит</t>
+        </is>
+      </c>
+      <c r="F11" s="28" t="inlineStr">
+        <is>
+          <t>Проверено 25.09.2026: закрытие 25 сентября показывает 4 записи, требующие решения</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="13">
+      <c r="A12" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>Администратор</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>Новый график мастера с даты</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>A-19 → A-22 → A-22p → [Сохранить график] → A-22</t>
+        </is>
+      </c>
+      <c r="E12" s="28" t="inlineStr">
+        <is>
+          <t>Проходит</t>
+        </is>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
+        <is>
+          <t>Проверено 25.09.2026: график ср–сб 11:00–18:00 с 25 сентября показывает запись, которая в него не попадает</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="13">
+      <c r="A13" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>Администратор</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>Фото работ после визита и публикация</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>A-01 → A-03 → A-12 → [Профиль мастера] → PUB-05</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>Проходит</t>
+        </is>
+      </c>
+      <c r="F13" s="28" t="inlineStr">
+        <is>
+          <t>Второй вход: A-09 → A-12. Без согласия клиента публикация блокируется</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="E2:E100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">

--- a/docs/karta-svyazey-prototipa.xlsx
+++ b/docs/karta-svyazey-prototipa.xlsx
@@ -1405,7 +1405,7 @@
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>Вход клиента (номер телефона)</t>
+          <t>Вход клиента (телефон или e-mail и пароль; вход по коду из SMS)</t>
         </is>
       </c>
       <c r="D4" s="27" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="I4" s="28" t="inlineStr">
         <is>
-          <t>Другое название</t>
+          <t>Совпадает</t>
         </is>
       </c>
       <c r="J4" s="29">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="N4" s="27" t="inlineStr">
         <is>
-          <t>Вход по телефону или e-mail и паролю (как в паспорте), а не по коду. Код из SMS — ссылкой «Войти по коду из SMS»</t>
+          <t>Вход по телефону или e-mail и паролю (как в паспорте), а не по коду. Код из SMS — ссылкой «Войти по коду из SMS» · 25.09.2026: ожидаемое название приведено к схеме БД — вход по телефону или e-mail и паролю (users.phone, users.email, users.password_hash)</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>Ввод кода из SMS (клиент)</t>
+          <t>Подтверждение кодом (телефон, e-mail, вход по коду, сброс пароля)</t>
         </is>
       </c>
       <c r="D5" s="27" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="I5" s="28" t="inlineStr">
         <is>
-          <t>Другое название</t>
+          <t>Совпадает</t>
         </is>
       </c>
       <c r="J5" s="29">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="N5" s="27" t="inlineStr">
         <is>
-          <t>Один экран кода на все случаи: регистрация, вход по SMS, вход сотрудника, восстановление пароля. Код в демо — 1234</t>
+          <t>Один экран кода на все случаи: регистрация, вход по SMS, вход сотрудника, восстановление пароля. Код в демо — 1234 · 25.09.2026: ожидаемое название приведено к схеме БД — одноразовые коды хранятся хешем (auth_codes)</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>Регистрация / заполнение профиля</t>
+          <t>Регистрация (имя, телефон, e-mail, пароль, согласия)</t>
         </is>
       </c>
       <c r="D6" s="27" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="I6" s="28" t="inlineStr">
         <is>
-          <t>Другое название</t>
+          <t>Совпадает</t>
         </is>
       </c>
       <c r="J6" s="29">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="N6" s="27" t="inlineStr">
         <is>
-          <t>Порядок обратный карте: сначала регистрация (имя, телефон, e-mail, пароль, согласие на обработку ПДн), потом код AUTH-02</t>
+          <t>Порядок обратный карте: сначала регистрация (имя, телефон, e-mail, пароль, согласие на обработку ПДн), потом код AUTH-02 · 25.09.2026: ожидаемое название приведено к схеме БД — согласие на обработку ПДн с редакцией политики, согласие на новости (users.pd_consent_*, marketing_consent_at)</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2868,7 @@
       <c r="M27" s="27" t="n"/>
       <c r="N27" s="27" t="inlineStr">
         <is>
-          <t>Кнопки: «Перенести», «Визит завершён», «Отметить неявку», «Отменить», «Открыть карточку клиента». «Подтвердить» и «Принять оплату» нет · 25.09.2026: у завершённой записи — «Фото работ» (A-12); время записи показывает уборку до …</t>
+          <t>Кнопки: «Перенести», «Визит завершён», «Отметить неявку», «Отменить», «Открыть карточку клиента». «Подтвердить» и «Принять оплату» нет · 25.09.2026: у завершённой записи — «Фото работ» (A-12); время записи показывает уборку до … · 25.09.2026: «Визит завершён» и «Отметить неявку» — только для визита, который уже начался; у записей не из демо-дня в поповере показывается дата</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       <c r="M33" s="27" t="n"/>
       <c r="N33" s="27" t="inlineStr">
         <is>
-          <t>Вкладки: история, предстоящие, заметки, важное. «Написать» нет. «Архивировать» убрана 25.09.2026: архива клиентов нет в паспорте, записи и история не удаляются · 25.09.2026: в истории визитов — «N фото» / «+ Добавить фото» (A-12)</t>
+          <t>Вкладки: история, предстоящие, заметки, важное. «Написать» нет. «Архивировать» убрана 25.09.2026: архива клиентов нет в паспорте, записи и история не удаляются · 25.09.2026: в истории визитов — «N фото» / «+ Добавить фото» (A-12) · 25.09.2026: предстоящие записи кликабельны и открывают поповер записи A-03</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3470,7 @@
       <c r="M37" s="27" t="n"/>
       <c r="N37" s="27" t="inlineStr">
         <is>
-          <t>Услуги и график — только просмотр · 25.09.2026: переключатель уровня «Мастер / Топ-мастер», цены услуг по уровню, «Новый график с даты» (A-22p)</t>
+          <t>Имя, статус, специализация; переключатель уровня «Мастер / Топ-мастер» и цены услуг по уровню (masters.level); рабочие дни и часы; форма «Новый график с даты» (A-22p, master_weekly_hours.valid_from). Обновлено 25.09.2026 при сверке со схемой БД</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="I47" s="28" t="inlineStr">
         <is>
-          <t>Лишняя в проекте</t>
+          <t>Совпадает</t>
         </is>
       </c>
       <c r="J47" s="29">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="N47" s="27" t="inlineStr">
         <is>
-          <t>После кода из AUTH-02. Состояния: форма, «Пароль изменён», «Ссылка больше не действует»</t>
+          <t>После кода из AUTH-02. Состояния: форма, «Пароль изменён», «Ссылка больше не действует» · 25.09.2026: входит в продукт по схеме БД — сброс пароля по одноразовому коду или ссылке (auth_codes, users.password_hash)</t>
         </is>
       </c>
     </row>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="I48" s="28" t="inlineStr">
         <is>
-          <t>Лишняя в проекте</t>
+          <t>Совпадает</t>
         </is>
       </c>
       <c r="J48" s="29">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="N48" s="27" t="inlineStr">
         <is>
-          <t>Через 10 минут удержания слота</t>
+          <t>Через 10 минут удержания слота · 25.09.2026: входит в продукт по схеме БД — бронь времени на 10 минут (slot_holds)</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="I49" s="28" t="inlineStr">
         <is>
-          <t>Лишняя в проекте</t>
+          <t>Совпадает</t>
         </is>
       </c>
       <c r="J49" s="29">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="N49" s="27" t="inlineStr">
         <is>
-          <t>Сценарий «Сессия истекла» в панели разработчика</t>
+          <t>Сценарий «Сессия истекла» в панели разработчика · 25.09.2026: входит в продукт по схеме БД — серверные сессии с истечением (sessions.expires_at)</t>
         </is>
       </c>
     </row>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="I50" s="28" t="inlineStr">
         <is>
-          <t>Лишняя в проекте</t>
+          <t>Совпадает</t>
         </is>
       </c>
       <c r="J50" s="29">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="N50" s="27" t="inlineStr">
         <is>
-          <t>Клик по карточке услуги</t>
+          <t>Клик по карточке услуги · 25.09.2026: входит в продукт по схеме БД — описание, длительность и цена услуги (services)</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="I51" s="28" t="inlineStr">
         <is>
-          <t>Лишняя в проекте</t>
+          <t>Совпадает</t>
         </is>
       </c>
       <c r="J51" s="29">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="N51" s="27" t="inlineStr">
         <is>
-          <t>Когда мастер выбран раньше услуг</t>
+          <t>Когда мастер выбран раньше услуг · 25.09.2026: входит в продукт по схеме БД — мастер должен выполнять все услуги визита (master_services)</t>
         </is>
       </c>
     </row>
@@ -4387,7 +4387,7 @@
       </c>
       <c r="I52" s="28" t="inlineStr">
         <is>
-          <t>Лишняя в проекте</t>
+          <t>Совпадает</t>
         </is>
       </c>
       <c r="J52" s="29">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="N52" s="27" t="inlineStr">
         <is>
-          <t>Логотип в шапке записи или «← Назад» на шаге услуг</t>
+          <t>Логотип в шапке записи или «← Назад» на шаге услуг · 25.09.2026: входит в продукт по схеме БД — при выходе бронь клиента удаляется (slot_holds)</t>
         </is>
       </c>
     </row>
@@ -4452,7 +4452,7 @@
       </c>
       <c r="I53" s="28" t="inlineStr">
         <is>
-          <t>Лишняя в проекте</t>
+          <t>Совпадает</t>
         </is>
       </c>
       <c r="J53" s="29">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="N53" s="27" t="inlineStr">
         <is>
-          <t>Подтверждение словом «УДАЛИТЬ»</t>
+          <t>Подтверждение словом «УДАЛИТЬ» · 25.09.2026: входит в продукт по схеме БД — удаление аккаунта — обезличивание (users.deleted_at), паспорт: функция клиента 9, сценарий 17</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="I55" s="28" t="inlineStr">
         <is>
-          <t>Лишняя в проекте</t>
+          <t>Совпадает</t>
         </is>
       </c>
       <c r="J55" s="29">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="N55" s="27" t="inlineStr">
         <is>
-          <t>Телефон студии для записи</t>
+          <t>Телефон студии для записи · 25.09.2026: входит в продукт по схеме БД — режим технических работ (settings.is_maintenance), паспорт: функция администратора 10</t>
         </is>
       </c>
     </row>
@@ -5745,15 +5745,19 @@
           <t>PUB-01, PUB-05</t>
         </is>
       </c>
-      <c r="I14" s="27" t="n"/>
+      <c r="I14" s="27" t="inlineStr">
+        <is>
+          <t>25.09.2026: данные есть: settings.phone, map_url, vk_url, telegram_url. Нужно сделать ссылки в подвале лендинга</t>
+        </is>
+      </c>
       <c r="J14" s="28" t="inlineStr">
         <is>
-          <t>Нет элемента</t>
+          <t>Связано</t>
         </is>
       </c>
       <c r="K14" s="27" t="inlineStr">
         <is>
-          <t>В подвале телефон и соцсети — текст без ссылок. Кнопка «Позвонить» — в секции «Контакты»</t>
+          <t>В подвале: адрес → карта, телефон → tel:, VK и Telegram → ссылки. В секции «Контакты» то же, карта-заглушка стала ссылкой «Открыть на карте». Сделано 25.09.2026</t>
         </is>
       </c>
     </row>
@@ -6413,10 +6417,14 @@
           <t>Все страницы M</t>
         </is>
       </c>
-      <c r="I27" s="27" t="n"/>
+      <c r="I27" s="27" t="inlineStr">
+        <is>
+          <t>25.09.2026: кабинета мастера нет ни в паспорте, ни в схеме БД (у мастеров нет учетных записей)</t>
+        </is>
+      </c>
       <c r="J27" s="28" t="inlineStr">
         <is>
-          <t>Нет элемента</t>
+          <t>Не нужно</t>
         </is>
       </c>
       <c r="K27" s="27" t="inlineStr">
@@ -6465,10 +6473,14 @@
           <t>Все страницы M</t>
         </is>
       </c>
-      <c r="I28" s="27" t="n"/>
+      <c r="I28" s="27" t="inlineStr">
+        <is>
+          <t>25.09.2026: кабинета мастера нет ни в паспорте, ни в схеме БД (у мастеров нет учетных записей)</t>
+        </is>
+      </c>
       <c r="J28" s="28" t="inlineStr">
         <is>
-          <t>Нет элемента</t>
+          <t>Не нужно</t>
         </is>
       </c>
       <c r="K28" s="27" t="inlineStr">
@@ -6777,15 +6789,19 @@
           <t>Все страницы A с меню</t>
         </is>
       </c>
-      <c r="I34" s="27" t="n"/>
+      <c r="I34" s="27" t="inlineStr">
+        <is>
+          <t>25.09.2026: данные есть: поиск клиентов по имени и телефону (users). Нужно открыть панель A-08 по результату поиска</t>
+        </is>
+      </c>
       <c r="J34" s="28" t="inlineStr">
         <is>
-          <t>Нет элемента</t>
+          <t>Связано</t>
         </is>
       </c>
       <c r="K34" s="27" t="inlineStr">
         <is>
-          <t>Поле «Поиск клиента» есть, но панель клиента не открывает</t>
+          <t>Поиск по имени или телефону показывает список клиентов; клик открывает панель клиента A-08. Сделано 25.09.2026</t>
         </is>
       </c>
     </row>
@@ -7319,17 +7335,17 @@
       </c>
       <c r="I6" s="27" t="inlineStr">
         <is>
-          <t>Если работа подписана мастером</t>
+          <t>Если работа подписана мастером · 25.09.2026: данные для перехода есть: фото → мастер (work_photos.master_id или через booking_item_id → bookings.master_id). Нужно сделать работы кликабельными в прототипе</t>
         </is>
       </c>
       <c r="J6" s="28" t="inlineStr">
         <is>
-          <t>Нет элемента</t>
+          <t>Связано</t>
         </is>
       </c>
       <c r="K6" s="27" t="inlineStr">
         <is>
-          <t>Работы в галерее не кликабельны; «Смотреть все работы →» ведёт в никуда (href="#")</t>
+          <t>Работа в галерее «Наши работы» открывает профиль мастера (#/masters/:id); подпись «Мастер →» на карточке. «Смотреть все работы» заменено на «Работы каждого мастера — в его профиле» (→ #masters). Сделано 25.09.2026</t>
         </is>
       </c>
     </row>
@@ -9432,15 +9448,19 @@
         <f>IF(G47="ANCHOR","Прокрутка к секции",IF(G47="EXT","Внешняя ссылка",IF(G47="PARENT","Вернуться туда, откуда открыто",IFERROR(INDEX(Реестр!$C:$C,MATCH(G47,Реестр!$A:$A,0)),"⚠ нет в реестре"))))</f>
         <v/>
       </c>
-      <c r="I47" s="27" t="n"/>
+      <c r="I47" s="27" t="inlineStr">
+        <is>
+          <t>25.09.2026: данные есть: bookings.master_id → masters. Нужно сделать имя мастера ссылкой в прототипе</t>
+        </is>
+      </c>
       <c r="J47" s="28" t="inlineStr">
         <is>
-          <t>Нет элемента</t>
+          <t>Связано</t>
         </is>
       </c>
       <c r="K47" s="27" t="inlineStr">
         <is>
-          <t>Имя мастера — текст</t>
+          <t>Имя мастера в карточке записи — ссылка на #/masters/:id. Сделано 25.09.2026</t>
         </is>
       </c>
     </row>
@@ -10232,10 +10252,14 @@
         <f>IF(G63="ANCHOR","Прокрутка к секции",IF(G63="EXT","Внешняя ссылка",IF(G63="PARENT","Вернуться туда, откуда открыто",IFERROR(INDEX(Реестр!$C:$C,MATCH(G63,Реестр!$A:$A,0)),"⚠ нет в реестре"))))</f>
         <v/>
       </c>
-      <c r="I63" s="27" t="n"/>
+      <c r="I63" s="27" t="inlineStr">
+        <is>
+          <t>25.09.2026: в схеме БД нет статуса подтверждения — запись сразу «Активна»</t>
+        </is>
+      </c>
       <c r="J63" s="28" t="inlineStr">
         <is>
-          <t>Нет элемента</t>
+          <t>Не нужно</t>
         </is>
       </c>
       <c r="K63" s="27" t="inlineStr">
@@ -11114,15 +11138,19 @@
         <f>IF(G81="ANCHOR","Прокрутка к секции",IF(G81="EXT","Внешняя ссылка",IF(G81="PARENT","Вернуться туда, откуда открыто",IFERROR(INDEX(Реестр!$C:$C,MATCH(G81,Реестр!$A:$A,0)),"⚠ нет в реестре"))))</f>
         <v/>
       </c>
-      <c r="I81" s="27" t="n"/>
+      <c r="I81" s="27" t="inlineStr">
+        <is>
+          <t>25.09.2026: данные есть: предстоящие записи клиента (bookings). Нужно открыть поповер по клику в прототипе</t>
+        </is>
+      </c>
       <c r="J81" s="28" t="inlineStr">
         <is>
-          <t>Нет элемента</t>
+          <t>Связано</t>
         </is>
       </c>
       <c r="K81" s="27" t="inlineStr">
         <is>
-          <t>Строки предстоящих записей не кликабельны</t>
+          <t>Строка во вкладке «Предстоящие» открывает поповер записи; список считается из записей клиента (в демо — запись Ольги Петровой на 6 октября). Сделано 25.09.2026</t>
         </is>
       </c>
     </row>
